--- a/data/VISTAAR CASE TRAKER - NAGERCOIL.xlsx
+++ b/data/VISTAAR CASE TRAKER - NAGERCOIL.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="111" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF784502-6B71-4516-BF56-BC119C9B2C4C}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3305C7EA-967A-4D75-B574-3EF2B817A5ED}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1797,7 +1797,7 @@
         <v>46213</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J11" s="43">
         <v>46213</v>
